--- a/website/examples/example_odk_calibrated_scale_Range.xlsx
+++ b/website/examples/example_odk_calibrated_scale_Range.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R3b18f5ea486e40b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rff22cf97b91f4ad3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rf5b8ec0ccf3b40c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rc6e6e44f209e4a0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R2eacf70e425245d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R6b6832e528e949b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -567,7 +567,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='calibrated_scale',input_prompt='Rate your pain',input_hint='0 means no pain; 100 means the worst pain you can imagine',input_vas_length_mm='50',input_use_range='true',input_lower_label='Least pain',input_upper_label='Worst pain',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='calibrated_scale',input_prompt='Rate your pain',input_hint='0 means no pain; 100 means the worst pain you can imagine',input_vas_length_mm='50',input_use_range='true',input_lower_label='Least pain',input_upper_label='Worst pain',return_mode='flat')</x:v>
       </x:c>
       <x:c r="J3"/>
       <x:c r="K3"/>
@@ -600,10 +600,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D5"/>
       <x:c r="E5"/>
@@ -621,10 +621,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D6"/>
       <x:c r="E6"/>
